--- a/output_5b.xlsx
+++ b/output_5b.xlsx
@@ -872,19 +872,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -892,19 +892,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -912,19 +912,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -932,19 +932,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -952,19 +952,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -972,19 +972,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -992,19 +992,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1015,16 +1015,16 @@
         <v>300</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
         <v>600</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1032,19 +1032,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1052,19 +1052,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1072,19 +1072,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -1092,19 +1092,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1112,19 +1112,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -1132,19 +1132,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -1155,16 +1155,16 @@
         <v>121</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
         <v>242</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -1172,19 +1172,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1192,19 +1192,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -1212,19 +1212,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -1232,7 +1232,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C20" t="n">
         <v>444</v>
@@ -1241,7 +1241,7 @@
         <v>7.4</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F20" t="n">
         <v>888</v>
@@ -1252,19 +1252,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -1275,16 +1275,16 @@
         <v>121</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
         <v>242</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -1292,19 +1292,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -1312,19 +1312,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -1332,19 +1332,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -1352,19 +1352,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -1372,19 +1372,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -1392,19 +1392,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="29">
@@ -1412,19 +1412,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -1432,7 +1432,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>

--- a/output_5b.xlsx
+++ b/output_5b.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cost per Part" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Overtime" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Overtime" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Backorders" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Production Plan" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Inventory Plan" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Setup Decisions" sheetId="6" state="visible" r:id="rId6"/>
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>129500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="3">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>361468.2</v>
+        <v>362060.6</v>
       </c>
     </row>
     <row r="4">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1084</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33780</v>
+        <v>21180</v>
       </c>
     </row>
     <row r="8">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="9">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527720.2</v>
+        <v>535590.6</v>
       </c>
     </row>
     <row r="10">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.52</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="12">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="13">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.9882</v>
       </c>
     </row>
   </sheetData>
@@ -564,260 +564,638 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Part</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Num Setups</t>
+          <t>OT Units X</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Setup Cost (EUR)</t>
+          <t>OT Minutes Y</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Holding Cost (EUR)</t>
+          <t>OT Hours Y</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Total Cost (EUR)</t>
+          <t>OT Cost X (EUR)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Overtime Cost X (EUR)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Overtime Cost Y (EUR)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Modernization Cost X (EUR)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Modernization Cost Y (EUR)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Backorder Cost (EUR)</t>
+          <t>OT Cost Y (EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B1401</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>300</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>600</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="C2" t="n">
-        <v>27500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37030</v>
-      </c>
-      <c r="E2" t="n">
-        <v>64530</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B2302</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" t="n">
-        <v>17500</v>
-      </c>
-      <c r="D3" t="n">
-        <v>18638.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>36138.2</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B3201</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>26000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>46800</v>
-      </c>
-      <c r="E4" t="n">
-        <v>72800</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B4702</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>38400</v>
-      </c>
-      <c r="E5" t="n">
-        <v>48400</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>V1501</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>79360</v>
-      </c>
-      <c r="E6" t="n">
-        <v>89360</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>V6302</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16000</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E2801</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>22500</v>
-      </c>
-      <c r="D8" t="n">
-        <v>141240</v>
-      </c>
-      <c r="E8" t="n">
-        <v>163740</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>39</v>
-      </c>
-      <c r="C9" t="n">
-        <v>129500</v>
-      </c>
-      <c r="D9" t="n">
-        <v>361468.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>490968.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1084</v>
-      </c>
-      <c r="G9" t="n">
-        <v>888</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>33780</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -832,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,27 +1221,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>OT Units X</t>
+          <t>Backorder (units)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>OT Minutes Y</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>OT Hours Y</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>OT Cost X (EUR)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>OT Cost Y (EUR)</t>
+          <t>Backorder Cost (EUR)</t>
         </is>
       </c>
     </row>
@@ -872,19 +1235,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -892,19 +1246,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -912,19 +1257,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -932,19 +1268,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -952,19 +1279,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -972,19 +1290,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -992,19 +1301,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1012,19 +1312,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>600</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1032,19 +1323,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1052,19 +1334,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1072,19 +1345,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1092,19 +1356,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1112,19 +1367,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1132,19 +1378,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1152,19 +1389,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>242</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1172,19 +1400,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1192,19 +1411,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1212,19 +1422,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1232,19 +1433,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>444</v>
-      </c>
-      <c r="D20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1252,19 +1444,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1272,19 +1455,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>242</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1292,19 +1466,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1312,19 +1477,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1332,19 +1488,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1352,19 +1499,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1372,19 +1510,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>-0</v>
+        <v>39</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="28">
@@ -1392,19 +1521,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1412,19 +1532,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1432,18 +1543,9 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1452,19 +1554,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>-0</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,7 +1738,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1657,16 +1750,16 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="G2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="H2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="I2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1675,16 +1768,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="M2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="N2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="O2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1693,13 +1786,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4084</v>
+        <v>3656</v>
       </c>
       <c r="S2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="T2" t="n">
-        <v>4232</v>
+        <v>3804</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1742,13 +1835,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1766,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5726</v>
+        <v>5706</v>
       </c>
       <c r="K3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1784,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="Q3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1799,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3174</v>
+        <v>2742</v>
       </c>
       <c r="V3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1851,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1872,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6126</v>
+        <v>5712</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1890,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1905,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4650</v>
+        <v>4224</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1936,7 +2029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22000</v>
+        <v>24100</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1957,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>21441</v>
+        <v>19992</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1975,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>21441</v>
+        <v>19971</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1990,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>16275</v>
+        <v>14784</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2039,13 +2132,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2004</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2066,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2084,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -2099,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3100</v>
+        <v>2816</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -2145,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2166,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3063</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2184,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3063</v>
+        <v>2853</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2199,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2325</v>
+        <v>2112</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2248,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2269,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1021</v>
+        <v>952</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2287,7 +2380,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1021</v>
+        <v>951</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2302,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>775</v>
+        <v>704</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -2320,97 +2413,194 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Forecast Demand E2801</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>136</v>
+      </c>
+      <c r="C9" t="n">
+        <v>144</v>
+      </c>
+      <c r="D9" t="n">
+        <v>263</v>
+      </c>
+      <c r="E9" t="n">
+        <v>123</v>
+      </c>
+      <c r="F9" t="n">
+        <v>171</v>
+      </c>
+      <c r="G9" t="n">
+        <v>195</v>
+      </c>
+      <c r="H9" t="n">
+        <v>414</v>
+      </c>
+      <c r="I9" t="n">
+        <v>147</v>
+      </c>
+      <c r="J9" t="n">
+        <v>129</v>
+      </c>
+      <c r="K9" t="n">
+        <v>245</v>
+      </c>
+      <c r="L9" t="n">
+        <v>208</v>
+      </c>
+      <c r="M9" t="n">
+        <v>178</v>
+      </c>
+      <c r="N9" t="n">
+        <v>168</v>
+      </c>
+      <c r="O9" t="n">
+        <v>208</v>
+      </c>
+      <c r="P9" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>168</v>
+      </c>
+      <c r="R9" t="n">
+        <v>181</v>
+      </c>
+      <c r="S9" t="n">
+        <v>188</v>
+      </c>
+      <c r="T9" t="n">
+        <v>212</v>
+      </c>
+      <c r="U9" t="n">
+        <v>253</v>
+      </c>
+      <c r="V9" t="n">
+        <v>219</v>
+      </c>
+      <c r="W9" t="n">
+        <v>196</v>
+      </c>
+      <c r="X9" t="n">
+        <v>226</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>239</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>183</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>149</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>167</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Realized Demand E2801</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>120</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>152</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>213</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>106</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>148</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>162</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>367</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>129</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>110</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>286</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>241</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>212</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N10" t="n">
         <v>199</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O10" t="n">
         <v>236</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P10" t="n">
         <v>187</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>186</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>193</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>201</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>228</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>237</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V10" t="n">
         <v>253</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W10" t="n">
         <v>209</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X10" t="n">
         <v>247</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y10" t="n">
         <v>233</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z10" t="n">
         <v>195</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA10" t="n">
         <v>192</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB10" t="n">
         <v>179</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC10" t="n">
         <v>171</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD10" t="n">
         <v>197</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE10" t="n">
         <v>228</v>
       </c>
     </row>
@@ -2598,10 +2788,10 @@
         <v>6400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2616,13 +2806,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="K2" t="n">
-        <v>8168</v>
+        <v>7608</v>
       </c>
       <c r="L2" t="n">
-        <v>12252</v>
+        <v>11412</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2634,13 +2824,13 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="Q2" t="n">
-        <v>8168</v>
+        <v>7608</v>
       </c>
       <c r="R2" t="n">
-        <v>12252</v>
+        <v>11412</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2652,10 +2842,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4084</v>
+        <v>3656</v>
       </c>
       <c r="W2" t="n">
-        <v>8168</v>
+        <v>7460</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -2695,31 +2885,31 @@
         <v>4000</v>
       </c>
       <c r="D3" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="F3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2737,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2752,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3174</v>
+        <v>2742</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2995,31 +3185,31 @@
         <v>3200</v>
       </c>
       <c r="G6" t="n">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="H6" t="n">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3174,91 +3364,91 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1230</v>
+        <v>1214</v>
       </c>
       <c r="C8" t="n">
-        <v>1728</v>
+        <v>1720</v>
       </c>
       <c r="D8" t="n">
-        <v>1515</v>
+        <v>1457</v>
       </c>
       <c r="E8" t="n">
-        <v>1409</v>
+        <v>1334</v>
       </c>
       <c r="F8" t="n">
-        <v>1261</v>
+        <v>1163</v>
       </c>
       <c r="G8" t="n">
-        <v>1099</v>
+        <v>968</v>
       </c>
       <c r="H8" t="n">
-        <v>732</v>
+        <v>554</v>
       </c>
       <c r="I8" t="n">
-        <v>603</v>
+        <v>407</v>
       </c>
       <c r="J8" t="n">
-        <v>1693</v>
+        <v>1578</v>
       </c>
       <c r="K8" t="n">
-        <v>1407</v>
+        <v>1333</v>
       </c>
       <c r="L8" t="n">
-        <v>1166</v>
+        <v>1125</v>
       </c>
       <c r="M8" t="n">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="N8" t="n">
-        <v>755</v>
+        <v>779</v>
       </c>
       <c r="O8" t="n">
-        <v>519</v>
+        <v>571</v>
       </c>
       <c r="P8" t="n">
-        <v>332</v>
+        <v>398</v>
       </c>
       <c r="Q8" t="n">
-        <v>1167</v>
+        <v>1182</v>
       </c>
       <c r="R8" t="n">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="S8" t="n">
-        <v>773</v>
+        <v>813</v>
       </c>
       <c r="T8" t="n">
-        <v>545</v>
+        <v>601</v>
       </c>
       <c r="U8" t="n">
-        <v>308</v>
+        <v>348</v>
       </c>
       <c r="V8" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="W8" t="n">
-        <v>867</v>
+        <v>884</v>
       </c>
       <c r="X8" t="n">
-        <v>620</v>
+        <v>658</v>
       </c>
       <c r="Y8" t="n">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="Z8" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>596</v>
+        <v>521</v>
       </c>
       <c r="AC8" t="n">
-        <v>425</v>
+        <v>372</v>
       </c>
       <c r="AD8" t="n">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -3442,7 +3632,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -3539,13 +3729,13 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3836,13 +4026,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>

--- a/output_5b.xlsx
+++ b/output_5b.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Production Plan" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Inventory Plan" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Setup Decisions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Backorders" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,7 +441,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>129500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="3">
@@ -450,7 +451,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>361468.2</v>
+        <v>360656.6</v>
       </c>
     </row>
     <row r="4">
@@ -460,7 +461,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1084</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5">
@@ -470,7 +471,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +481,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -490,7 +491,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33780</v>
+        <v>21180</v>
       </c>
     </row>
     <row r="8">
@@ -500,7 +501,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>37250</v>
       </c>
     </row>
     <row r="9">
@@ -510,7 +511,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527720.2</v>
+        <v>553686.6</v>
       </c>
     </row>
     <row r="10">
@@ -520,7 +521,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -530,27 +531,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.52</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Service Level</t>
+          <t>New capacity WS-X (units)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>New capacity WS-Y (min)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11412</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Service Level</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Fill Rate</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
+      <c r="B15" t="n">
+        <v>0.9752</v>
       </c>
     </row>
   </sheetData>
@@ -564,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,6 +639,11 @@
           <t>Backorder Cost (EUR)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Grand Total (EUR)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -626,22 +652,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>27500</v>
+        <v>30000</v>
       </c>
       <c r="D2" t="n">
-        <v>37030</v>
+        <v>41182</v>
       </c>
       <c r="E2" t="n">
-        <v>64530</v>
+        <v>71182</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -656,16 +683,17 @@
         <v>17500</v>
       </c>
       <c r="D3" t="n">
-        <v>18638.2</v>
+        <v>21107.8</v>
       </c>
       <c r="E3" t="n">
-        <v>36138.2</v>
+        <v>38607.8</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,6 +718,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -714,6 +743,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -728,16 +758,17 @@
         <v>10000</v>
       </c>
       <c r="D6" t="n">
-        <v>79360</v>
+        <v>69526.8</v>
       </c>
       <c r="E6" t="n">
-        <v>89360</v>
+        <v>79526.8</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -762,6 +793,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -776,16 +808,17 @@
         <v>22500</v>
       </c>
       <c r="D8" t="n">
-        <v>141240</v>
+        <v>143640</v>
       </c>
       <c r="E8" t="n">
-        <v>163740</v>
+        <v>166140</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -794,31 +827,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>129500</v>
+        <v>132000</v>
       </c>
       <c r="D9" t="n">
-        <v>361468.2</v>
+        <v>360656.6</v>
       </c>
       <c r="E9" t="n">
-        <v>490968.2</v>
+        <v>492656.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1084</v>
+        <v>600</v>
       </c>
       <c r="G9" t="n">
-        <v>888</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I9" t="n">
-        <v>33780</v>
+        <v>21180</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>37250</v>
+      </c>
+      <c r="K9" t="n">
+        <v>553686.6</v>
       </c>
     </row>
   </sheetData>
@@ -875,16 +911,16 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -895,16 +931,16 @@
         <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -915,16 +951,16 @@
         <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>-0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -935,16 +971,16 @@
         <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>-0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -955,16 +991,16 @@
         <v>-0</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>-0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -975,16 +1011,16 @@
         <v>-0</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -995,16 +1031,16 @@
         <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1015,16 +1051,16 @@
         <v>300</v>
       </c>
       <c r="C9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>600</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1035,16 +1071,16 @@
         <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>-0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1055,16 +1091,16 @@
         <v>-0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1075,16 +1111,16 @@
         <v>-0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>-0</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1131,16 @@
         <v>-0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>-0</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1115,16 +1151,16 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1135,16 +1171,16 @@
         <v>-0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>-0</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1152,19 +1188,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>121</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>242</v>
+        <v>-0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1175,16 +1211,16 @@
         <v>-0</v>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>-0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1195,16 +1231,16 @@
         <v>-0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>-0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1215,16 +1251,16 @@
         <v>-0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>-0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1235,16 +1271,16 @@
         <v>-0</v>
       </c>
       <c r="C20" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>-0</v>
       </c>
       <c r="F20" t="n">
-        <v>888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1255,16 +1291,16 @@
         <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>-0</v>
       </c>
       <c r="F21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1272,19 +1308,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>121</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>242</v>
+        <v>-0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1295,16 +1331,16 @@
         <v>-0</v>
       </c>
       <c r="C23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>-0</v>
       </c>
       <c r="F23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1315,16 +1351,16 @@
         <v>-0</v>
       </c>
       <c r="C24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1335,16 +1371,16 @@
         <v>-0</v>
       </c>
       <c r="C25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>-0</v>
       </c>
       <c r="F25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1355,16 +1391,16 @@
         <v>-0</v>
       </c>
       <c r="C26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1375,16 +1411,16 @@
         <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1395,16 +1431,16 @@
         <v>-0</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>-0</v>
       </c>
       <c r="F28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1415,16 +1451,16 @@
         <v>-0</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>-0</v>
       </c>
       <c r="F29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1478,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,7 +1681,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1657,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="G2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="H2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="I2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1675,16 +1711,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="M2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="N2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="O2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1693,13 +1729,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4084</v>
+        <v>3656</v>
       </c>
       <c r="S2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="T2" t="n">
-        <v>4232</v>
+        <v>3804</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1742,13 +1778,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1766,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5726</v>
+        <v>5706</v>
       </c>
       <c r="K3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1784,10 +1820,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="Q3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1799,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3174</v>
+        <v>2742</v>
       </c>
       <c r="V3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1851,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1872,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6126</v>
+        <v>5712</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1890,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1905,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4650</v>
+        <v>4224</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1936,7 +1972,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22000</v>
+        <v>24100</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1957,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>21441</v>
+        <v>19992</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1975,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>21441</v>
+        <v>19971</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1990,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>16275</v>
+        <v>14784</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2039,13 +2075,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2004</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2066,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2084,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -2099,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3100</v>
+        <v>2816</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -2145,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2166,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3063</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2184,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3063</v>
+        <v>2853</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2199,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2325</v>
+        <v>2112</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2248,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2269,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1021</v>
+        <v>952</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2287,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1021</v>
+        <v>951</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2302,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>775</v>
+        <v>704</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -2320,97 +2356,194 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Forecast Demand E2801</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>136</v>
+      </c>
+      <c r="C9" t="n">
+        <v>144</v>
+      </c>
+      <c r="D9" t="n">
+        <v>263</v>
+      </c>
+      <c r="E9" t="n">
+        <v>123</v>
+      </c>
+      <c r="F9" t="n">
+        <v>171</v>
+      </c>
+      <c r="G9" t="n">
+        <v>195</v>
+      </c>
+      <c r="H9" t="n">
+        <v>414</v>
+      </c>
+      <c r="I9" t="n">
+        <v>147</v>
+      </c>
+      <c r="J9" t="n">
+        <v>129</v>
+      </c>
+      <c r="K9" t="n">
+        <v>245</v>
+      </c>
+      <c r="L9" t="n">
+        <v>208</v>
+      </c>
+      <c r="M9" t="n">
+        <v>178</v>
+      </c>
+      <c r="N9" t="n">
+        <v>168</v>
+      </c>
+      <c r="O9" t="n">
+        <v>208</v>
+      </c>
+      <c r="P9" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>168</v>
+      </c>
+      <c r="R9" t="n">
+        <v>181</v>
+      </c>
+      <c r="S9" t="n">
+        <v>188</v>
+      </c>
+      <c r="T9" t="n">
+        <v>212</v>
+      </c>
+      <c r="U9" t="n">
+        <v>253</v>
+      </c>
+      <c r="V9" t="n">
+        <v>219</v>
+      </c>
+      <c r="W9" t="n">
+        <v>196</v>
+      </c>
+      <c r="X9" t="n">
+        <v>226</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>239</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>183</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>149</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>167</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Realized Demand E2801</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>120</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>152</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>213</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>106</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>148</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>162</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>367</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>129</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>110</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>286</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>241</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>212</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N10" t="n">
         <v>199</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O10" t="n">
         <v>236</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P10" t="n">
         <v>187</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>186</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>193</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>201</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>228</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>237</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V10" t="n">
         <v>253</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W10" t="n">
         <v>209</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X10" t="n">
         <v>247</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y10" t="n">
         <v>233</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z10" t="n">
         <v>195</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA10" t="n">
         <v>192</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB10" t="n">
         <v>179</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC10" t="n">
         <v>171</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD10" t="n">
         <v>197</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE10" t="n">
         <v>228</v>
       </c>
     </row>
@@ -2598,10 +2731,10 @@
         <v>6400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2616,13 +2749,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="K2" t="n">
-        <v>8168</v>
+        <v>7608</v>
       </c>
       <c r="L2" t="n">
-        <v>12252</v>
+        <v>11412</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2634,13 +2767,13 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4084</v>
+        <v>3804</v>
       </c>
       <c r="Q2" t="n">
-        <v>8168</v>
+        <v>7608</v>
       </c>
       <c r="R2" t="n">
-        <v>12252</v>
+        <v>11412</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2652,10 +2785,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4084</v>
+        <v>3656</v>
       </c>
       <c r="W2" t="n">
-        <v>8168</v>
+        <v>7460</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -2695,31 +2828,31 @@
         <v>4000</v>
       </c>
       <c r="D3" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="F3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2737,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6126</v>
+        <v>5706</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2752,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3174</v>
+        <v>2742</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2995,31 +3128,31 @@
         <v>3200</v>
       </c>
       <c r="G6" t="n">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="H6" t="n">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3198,67 +3331,67 @@
         <v>603</v>
       </c>
       <c r="J8" t="n">
-        <v>1693</v>
+        <v>1793</v>
       </c>
       <c r="K8" t="n">
-        <v>1407</v>
+        <v>1507</v>
       </c>
       <c r="L8" t="n">
-        <v>1166</v>
+        <v>1266</v>
       </c>
       <c r="M8" t="n">
-        <v>954</v>
+        <v>1054</v>
       </c>
       <c r="N8" t="n">
-        <v>755</v>
+        <v>855</v>
       </c>
       <c r="O8" t="n">
-        <v>519</v>
+        <v>619</v>
       </c>
       <c r="P8" t="n">
-        <v>332</v>
+        <v>432</v>
       </c>
       <c r="Q8" t="n">
-        <v>1167</v>
+        <v>1198</v>
       </c>
       <c r="R8" t="n">
-        <v>974</v>
+        <v>1005</v>
       </c>
       <c r="S8" t="n">
-        <v>773</v>
+        <v>804</v>
       </c>
       <c r="T8" t="n">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="U8" t="n">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="V8" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="W8" t="n">
-        <v>867</v>
+        <v>828</v>
       </c>
       <c r="X8" t="n">
-        <v>620</v>
+        <v>581</v>
       </c>
       <c r="Y8" t="n">
-        <v>387</v>
+        <v>348</v>
       </c>
       <c r="Z8" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>596</v>
+        <v>486</v>
       </c>
       <c r="AC8" t="n">
-        <v>425</v>
+        <v>315</v>
       </c>
       <c r="AD8" t="n">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -3442,7 +3575,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -3539,13 +3672,13 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3836,13 +3969,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4112,6 +4245,274 @@
       </c>
       <c r="AE8" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>W27</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>W28</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>W29</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Backorder E2801</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
